--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_PARTIZAN MOZZART BET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_PARTIZAN MOZZART BET BELGRADE.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>20.6186</v>
+        <v>29.3564</v>
       </c>
       <c r="E2" t="n">
-        <v>15.2068</v>
+        <v>18.1551</v>
       </c>
       <c r="F2" t="n">
-        <v>5.412000000000001</v>
+        <v>11.2013</v>
       </c>
       <c r="G2" t="n">
-        <v>-27.1977</v>
+        <v>13.5063</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09020000000000028</v>
+        <v>7.9287</v>
       </c>
       <c r="I2" t="n">
-        <v>-27.2882</v>
+        <v>5.5779</v>
       </c>
       <c r="J2" t="n">
-        <v>26.399</v>
+        <v>24.2386</v>
       </c>
       <c r="K2" t="n">
-        <v>28.1366</v>
+        <v>13.6371</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.7369</v>
+        <v>10.6013</v>
       </c>
       <c r="M2" t="n">
-        <v>-53.5965</v>
+        <v>-10.7322</v>
       </c>
       <c r="N2" t="n">
-        <v>-28.0459</v>
+        <v>-5.708600000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-25.5509</v>
+        <v>-5.0236</v>
       </c>
       <c r="P2" t="n">
-        <v>15.7731</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q2" t="n">
-        <v>-61.4677</v>
+        <v>-32.7054</v>
       </c>
       <c r="R2" t="n">
-        <v>77.2402</v>
+        <v>31.3137</v>
       </c>
       <c r="S2" t="n">
-        <v>23.0405</v>
+        <v>2.7671</v>
       </c>
       <c r="T2" t="n">
-        <v>8.981400000000001</v>
+        <v>-0.4981000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>14.0594</v>
+        <v>3.2652</v>
       </c>
       <c r="V2" t="n">
-        <v>9.0029</v>
+        <v>14.4747</v>
       </c>
       <c r="W2" t="n">
-        <v>41.2932</v>
+        <v>27.1197</v>
       </c>
       <c r="X2" t="n">
-        <v>-32.2904</v>
+        <v>-12.645</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>20.5088</v>
+        <v>10.2421</v>
       </c>
       <c r="E3" t="n">
-        <v>13.4922</v>
+        <v>6.934399999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>7.0168</v>
+        <v>3.307600000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>13.5063</v>
+        <v>-27.1977</v>
       </c>
       <c r="H3" t="n">
-        <v>7.9287</v>
+        <v>0.09020000000000028</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5779</v>
+        <v>-27.2882</v>
       </c>
       <c r="J3" t="n">
-        <v>24.2386</v>
+        <v>26.399</v>
       </c>
       <c r="K3" t="n">
-        <v>13.6371</v>
+        <v>28.1366</v>
       </c>
       <c r="L3" t="n">
-        <v>10.6013</v>
+        <v>-1.7369</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.7322</v>
+        <v>-53.5965</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.708600000000001</v>
+        <v>-28.0459</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.0236</v>
+        <v>-25.5509</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3917</v>
+        <v>15.7731</v>
       </c>
       <c r="Q3" t="n">
-        <v>-32.7054</v>
+        <v>-61.4677</v>
       </c>
       <c r="R3" t="n">
-        <v>31.3137</v>
+        <v>77.2402</v>
       </c>
       <c r="S3" t="n">
-        <v>-6.0805</v>
+        <v>12.6639</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.1609</v>
+        <v>0.7089999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9194000000000001</v>
+        <v>11.9551</v>
       </c>
       <c r="V3" t="n">
-        <v>14.4747</v>
+        <v>9.0029</v>
       </c>
       <c r="W3" t="n">
-        <v>27.1197</v>
+        <v>41.2932</v>
       </c>
       <c r="X3" t="n">
-        <v>-12.645</v>
+        <v>-32.2904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>T. JEKIRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>20.0635</v>
+        <v>6.515199999999998</v>
       </c>
       <c r="E4" t="n">
-        <v>28.5795</v>
+        <v>-1.1093</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.516</v>
+        <v>7.6247</v>
       </c>
       <c r="G4" t="n">
-        <v>11.1071</v>
+        <v>-0.07959999999999995</v>
       </c>
       <c r="H4" t="n">
-        <v>15.0634</v>
+        <v>-5.4813</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.9563</v>
+        <v>5.4016</v>
       </c>
       <c r="J4" t="n">
-        <v>34.0641</v>
+        <v>7.182799999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>24.8995</v>
+        <v>-0.5829000000000008</v>
       </c>
       <c r="L4" t="n">
-        <v>9.164300000000001</v>
+        <v>7.7658</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.9569</v>
+        <v>-7.2625</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.8362</v>
+        <v>-4.8983</v>
       </c>
       <c r="O4" t="n">
-        <v>-13.1206</v>
+        <v>-2.3645</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.711199999999999</v>
+        <v>4.6394</v>
       </c>
       <c r="Q4" t="n">
-        <v>-32.2415</v>
+        <v>-17.3967</v>
       </c>
       <c r="R4" t="n">
-        <v>28.5303</v>
+        <v>22.0356</v>
       </c>
       <c r="S4" t="n">
-        <v>25.4719</v>
+        <v>9.6342</v>
       </c>
       <c r="T4" t="n">
-        <v>16.8409</v>
+        <v>3.2867</v>
       </c>
       <c r="U4" t="n">
-        <v>8.6309</v>
+        <v>6.3477</v>
       </c>
       <c r="V4" t="n">
-        <v>-12.8043</v>
+        <v>-7.6782</v>
       </c>
       <c r="W4" t="n">
-        <v>9.915900000000001</v>
+        <v>5.817500000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-22.7202</v>
+        <v>-13.4957</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. JEKIRI</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6936</v>
+        <v>4.382100000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>7.8039</v>
+        <v>15.2585</v>
       </c>
       <c r="F5" t="n">
-        <v>7.8899</v>
+        <v>-10.8765</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.07959999999999995</v>
+        <v>11.1071</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.4813</v>
+        <v>15.0634</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4016</v>
+        <v>-3.9563</v>
       </c>
       <c r="J5" t="n">
-        <v>7.182799999999999</v>
+        <v>34.0641</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5829000000000008</v>
+        <v>24.8995</v>
       </c>
       <c r="L5" t="n">
-        <v>7.7658</v>
+        <v>9.164300000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.2625</v>
+        <v>-22.9569</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.8983</v>
+        <v>-9.8362</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3645</v>
+        <v>-13.1206</v>
       </c>
       <c r="P5" t="n">
-        <v>4.6394</v>
+        <v>-3.711199999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-17.3967</v>
+        <v>-32.2415</v>
       </c>
       <c r="R5" t="n">
-        <v>22.0356</v>
+        <v>28.5303</v>
       </c>
       <c r="S5" t="n">
-        <v>18.8124</v>
+        <v>9.7904</v>
       </c>
       <c r="T5" t="n">
-        <v>12.2</v>
+        <v>3.5199</v>
       </c>
       <c r="U5" t="n">
-        <v>6.6124</v>
+        <v>6.2705</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.6782</v>
+        <v>-12.8043</v>
       </c>
       <c r="W5" t="n">
-        <v>5.817500000000001</v>
+        <v>9.915900000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.4957</v>
+        <v>-22.7202</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>M. NAKIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7909</v>
+        <v>0.4936</v>
       </c>
       <c r="E6" t="n">
-        <v>8.259600000000001</v>
+        <v>0.5422</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.469</v>
+        <v>-0.0485</v>
       </c>
       <c r="G6" t="n">
-        <v>3.804399999999999</v>
+        <v>0.4229</v>
       </c>
       <c r="H6" t="n">
-        <v>7.782900000000001</v>
+        <v>0.4261</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.978899999999999</v>
+        <v>-0.0033</v>
       </c>
       <c r="J6" t="n">
-        <v>28.2714</v>
+        <v>0.605</v>
       </c>
       <c r="K6" t="n">
-        <v>18.0895</v>
+        <v>0.605</v>
       </c>
       <c r="L6" t="n">
-        <v>10.1813</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-24.4669</v>
+        <v>-0.1821</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.3067</v>
+        <v>-0.1788</v>
       </c>
       <c r="O6" t="n">
-        <v>-14.1602</v>
+        <v>-0.0033</v>
       </c>
       <c r="P6" t="n">
-        <v>-21.5716</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-64.01909999999999</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>42.4478</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>24.8155</v>
+        <v>-0.1612</v>
       </c>
       <c r="T6" t="n">
-        <v>18.9076</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>5.9083</v>
+        <v>-0.0984</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.2577</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>25.0996</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-29.3574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NAKIC</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2577</v>
+        <v>-0.09519999999999929</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3063</v>
+        <v>4.992399999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0485</v>
+        <v>-5.087800000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4229</v>
+        <v>-39.1113</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4261</v>
+        <v>-20.5377</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0033</v>
+        <v>-18.5739</v>
       </c>
       <c r="J7" t="n">
-        <v>0.605</v>
+        <v>7.962900000000002</v>
       </c>
       <c r="K7" t="n">
-        <v>0.605</v>
+        <v>4.643800000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.3185</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1821</v>
+        <v>-47.074</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1788</v>
+        <v>-25.1813</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0033</v>
+        <v>-21.8926</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>34.3293</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-19.9485</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>54.2773</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3971</v>
+        <v>4.5279</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2987</v>
+        <v>-1.4224</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0984</v>
+        <v>5.9506</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1592999999999996</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>18.4003</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-18.241</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2699</v>
+        <v>-0.3809999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2272</v>
+        <v>-0.05199999999999998</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4971000000000001</v>
+        <v>-0.3290999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1016</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1357</v>
+        <v>0.02460000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3383</v>
+        <v>0.05910000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2026</v>
+        <v>-0.03449999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>M. MUURINEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5211</v>
+        <v>-2.6584</v>
       </c>
       <c r="E9" t="n">
-        <v>7.1827</v>
+        <v>-0.3428</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.703600000000002</v>
+        <v>-2.3157</v>
       </c>
       <c r="G9" t="n">
-        <v>-39.1113</v>
+        <v>-2.4132</v>
       </c>
       <c r="H9" t="n">
-        <v>-20.5377</v>
+        <v>-0.9241</v>
       </c>
       <c r="I9" t="n">
-        <v>-18.5739</v>
+        <v>-1.4888</v>
       </c>
       <c r="J9" t="n">
-        <v>7.962900000000002</v>
+        <v>-0.6655</v>
       </c>
       <c r="K9" t="n">
-        <v>4.643800000000001</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>3.3185</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-47.074</v>
+        <v>-1.7477</v>
       </c>
       <c r="N9" t="n">
-        <v>-25.1813</v>
+        <v>-1.0081</v>
       </c>
       <c r="O9" t="n">
-        <v>-21.8926</v>
+        <v>-0.7393</v>
       </c>
       <c r="P9" t="n">
-        <v>34.3293</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-19.9485</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>54.2773</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>3.102300000000001</v>
+        <v>-0.01079999999999992</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7676000000000005</v>
+        <v>0.1809</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3348</v>
+        <v>-0.1918</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1592999999999996</v>
+        <v>-0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>18.4003</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>-18.241</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MUURINEN</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4555</v>
+        <v>-5.063300000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8146</v>
+        <v>-5.300700000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.641</v>
+        <v>0.2368000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4132</v>
+        <v>-11.9022</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9241</v>
+        <v>-5.2805</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4888</v>
+        <v>-6.621700000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6655</v>
+        <v>3.527199999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08399999999999999</v>
+        <v>2.4681</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7495000000000001</v>
+        <v>1.0591</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7477</v>
+        <v>-15.4297</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0081</v>
+        <v>-7.7487</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7393</v>
+        <v>-7.6808</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>16.933</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-8.814499999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>25.7473</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8078</v>
+        <v>-1.8791</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2909</v>
+        <v>-2.4415</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5172</v>
+        <v>0.5623000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9304</v>
+        <v>-8.214399999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>2.428</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-10.6424</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>U. MIJAILOVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.477</v>
+        <v>-7.5863</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9414</v>
+        <v>-2.0511</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5357</v>
+        <v>-5.5354</v>
       </c>
       <c r="G11" t="n">
-        <v>-11.9022</v>
+        <v>-3.0985</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.2805</v>
+        <v>-1.1211</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.621700000000001</v>
+        <v>-1.9774</v>
       </c>
       <c r="J11" t="n">
-        <v>3.527199999999999</v>
+        <v>-0.6791</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4681</v>
+        <v>-0.7527</v>
       </c>
       <c r="L11" t="n">
-        <v>1.0591</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-15.4297</v>
+        <v>-2.4194</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.7487</v>
+        <v>-0.3683</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.6808</v>
+        <v>-2.051</v>
       </c>
       <c r="P11" t="n">
-        <v>16.933</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.814499999999999</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>25.7473</v>
+        <v>1.3918</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.2926</v>
+        <v>0.1052</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.0822</v>
+        <v>-0.2122</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2104</v>
+        <v>0.3174</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.214399999999999</v>
+        <v>-4.8249</v>
       </c>
       <c r="W11" t="n">
-        <v>2.428</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-10.6424</v>
+        <v>-4.8249</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U. MIJAILOVIC</t>
+          <t>C. PAYNE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8633</v>
+        <v>-7.838300000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3617</v>
+        <v>-5.5667</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.5017</v>
+        <v>-2.2718</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0985</v>
+        <v>-2.145199999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1211</v>
+        <v>1.3757</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9774</v>
+        <v>-3.521099999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6791</v>
+        <v>13.1992</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7527</v>
+        <v>8.206099999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0736</v>
+        <v>4.9931</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4194</v>
+        <v>-15.3444</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3683</v>
+        <v>-6.8304</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.051</v>
+        <v>-8.5143</v>
       </c>
       <c r="P12" t="n">
-        <v>0.232</v>
+        <v>-10.438</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-27.3703</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3918</v>
+        <v>16.9327</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1718</v>
+        <v>-1.9411</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5228</v>
+        <v>-3.2208</v>
       </c>
       <c r="U12" t="n">
-        <v>0.351</v>
+        <v>1.2799</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.8249</v>
+        <v>6.6857</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>11.8253</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.8249</v>
+        <v>-5.139600000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RADANOV</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.277</v>
+        <v>-9.391900000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.772699999999999</v>
+        <v>-23.0793</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.5046</v>
+        <v>13.687</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.9861</v>
+        <v>2.4536</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0981</v>
+        <v>-8.9305</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.8881</v>
+        <v>11.3841</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6331</v>
+        <v>50.5943</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8843000000000001</v>
+        <v>16.6636</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2512</v>
+        <v>33.9307</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.6192</v>
+        <v>-48.141</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9824</v>
+        <v>-25.5947</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.6369</v>
+        <v>-22.5464</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1598</v>
+        <v>-18.7881</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.4948</v>
+        <v>-93.0129</v>
       </c>
       <c r="R13" t="n">
-        <v>5.335</v>
+        <v>74.22490000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7008000000000001</v>
+        <v>-5.658</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9111</v>
+        <v>-8.8529</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2104</v>
+        <v>3.1949</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.4306</v>
+        <v>12.6002</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>28.1919</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.4306</v>
+        <v>-15.5917</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. PAYNE</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.3273</v>
+        <v>-11.4967</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.845600000000003</v>
+        <v>-2.764500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.4817</v>
+        <v>-8.7326</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.145199999999999</v>
+        <v>-6.2402</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3757</v>
+        <v>-6.582500000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.521099999999999</v>
+        <v>0.3425000000000011</v>
       </c>
       <c r="J14" t="n">
-        <v>13.1992</v>
+        <v>29.1572</v>
       </c>
       <c r="K14" t="n">
-        <v>8.206099999999999</v>
+        <v>11.1072</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9931</v>
+        <v>18.0499</v>
       </c>
       <c r="M14" t="n">
-        <v>-15.3444</v>
+        <v>-35.3971</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.8304</v>
+        <v>-17.6896</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.5143</v>
+        <v>-17.7074</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.438</v>
+        <v>-8.582000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-27.3703</v>
+        <v>-45.9267</v>
       </c>
       <c r="R14" t="n">
-        <v>16.9327</v>
+        <v>37.3445</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.4301</v>
+        <v>-3.1076</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.4999</v>
+        <v>-5.2461</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9299000000000001</v>
+        <v>2.1384</v>
       </c>
       <c r="V14" t="n">
-        <v>6.6857</v>
+        <v>6.4331</v>
       </c>
       <c r="W14" t="n">
-        <v>11.8253</v>
+        <v>19.251</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.139600000000001</v>
+        <v>-12.8179</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>A. RADANOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>-24.7791</v>
+        <v>-11.5659</v>
       </c>
       <c r="E15" t="n">
-        <v>-22.7112</v>
+        <v>-7.0952</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.068</v>
+        <v>-4.4706</v>
       </c>
       <c r="G15" t="n">
-        <v>-16.8852</v>
+        <v>-4.9861</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2287</v>
+        <v>-1.0981</v>
       </c>
       <c r="I15" t="n">
-        <v>-16.6567</v>
+        <v>-3.8881</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.547600000000001</v>
+        <v>0.6331</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9586</v>
+        <v>0.8843000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.5063</v>
+        <v>-0.2512</v>
       </c>
       <c r="M15" t="n">
-        <v>-14.3374</v>
+        <v>-5.6192</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.1873</v>
+        <v>-1.9824</v>
       </c>
       <c r="O15" t="n">
-        <v>-10.1499</v>
+        <v>-3.6369</v>
       </c>
       <c r="P15" t="n">
-        <v>7.422699999999999</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-16.469</v>
+        <v>-6.4948</v>
       </c>
       <c r="R15" t="n">
-        <v>23.8915</v>
+        <v>5.335</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.71</v>
+        <v>-0.9897</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.3033</v>
+        <v>-1.2337</v>
       </c>
       <c r="U15" t="n">
-        <v>3.5929</v>
+        <v>0.2441000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-13.6065</v>
+        <v>-4.4306</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-15.2148</v>
+        <v>-4.4306</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-28.1878</v>
+        <v>-14.9989</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.803</v>
+        <v>-8.4071</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.3848</v>
+        <v>-6.5917</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.2402</v>
+        <v>3.804399999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.582500000000001</v>
+        <v>7.782900000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3425000000000011</v>
+        <v>-3.978899999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>29.1572</v>
+        <v>28.2714</v>
       </c>
       <c r="K16" t="n">
-        <v>11.1072</v>
+        <v>18.0895</v>
       </c>
       <c r="L16" t="n">
-        <v>18.0499</v>
+        <v>10.1813</v>
       </c>
       <c r="M16" t="n">
-        <v>-35.3971</v>
+        <v>-24.4669</v>
       </c>
       <c r="N16" t="n">
-        <v>-17.6896</v>
+        <v>-10.3067</v>
       </c>
       <c r="O16" t="n">
-        <v>-17.7074</v>
+        <v>-14.1602</v>
       </c>
       <c r="P16" t="n">
-        <v>-8.582000000000001</v>
+        <v>-21.5716</v>
       </c>
       <c r="Q16" t="n">
-        <v>-45.9267</v>
+        <v>-64.01909999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>37.3445</v>
+        <v>42.4478</v>
       </c>
       <c r="S16" t="n">
-        <v>-19.7986</v>
+        <v>7.0262</v>
       </c>
       <c r="T16" t="n">
-        <v>-17.2847</v>
+        <v>2.2405</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.5141</v>
+        <v>4.7856</v>
       </c>
       <c r="V16" t="n">
-        <v>6.4331</v>
+        <v>-4.2577</v>
       </c>
       <c r="W16" t="n">
-        <v>19.251</v>
+        <v>25.0996</v>
       </c>
       <c r="X16" t="n">
-        <v>-12.8179</v>
+        <v>-29.3574</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D17" t="n">
-        <v>-29.9383</v>
+        <v>-23.4728</v>
       </c>
       <c r="E17" t="n">
-        <v>-23.1601</v>
+        <v>-20.6122</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.7781</v>
+        <v>-2.8616</v>
       </c>
       <c r="G17" t="n">
-        <v>-35.5159</v>
+        <v>-16.8852</v>
       </c>
       <c r="H17" t="n">
-        <v>-16.3231</v>
+        <v>-0.2287</v>
       </c>
       <c r="I17" t="n">
-        <v>-19.1926</v>
+        <v>-16.6567</v>
       </c>
       <c r="J17" t="n">
-        <v>-12.7585</v>
+        <v>-2.547600000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.5473</v>
+        <v>3.9586</v>
       </c>
       <c r="L17" t="n">
-        <v>-5.2109</v>
+        <v>-6.5063</v>
       </c>
       <c r="M17" t="n">
-        <v>-22.7573</v>
+        <v>-14.3374</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.7759</v>
+        <v>-4.1873</v>
       </c>
       <c r="O17" t="n">
-        <v>-13.9812</v>
+        <v>-10.1499</v>
       </c>
       <c r="P17" t="n">
-        <v>5.798999999999999</v>
+        <v>7.422699999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-16.2371</v>
+        <v>-16.469</v>
       </c>
       <c r="R17" t="n">
-        <v>22.0355</v>
+        <v>23.8915</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7361</v>
+        <v>-0.4039000000000004</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.420300000000001</v>
+        <v>-3.2041</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6842</v>
+        <v>2.8</v>
       </c>
       <c r="V17" t="n">
-        <v>1.514999999999999</v>
+        <v>-13.6065</v>
       </c>
       <c r="W17" t="n">
-        <v>9.2555</v>
+        <v>1.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.7404</v>
+        <v>-15.2148</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-32.0572</v>
+        <v>-23.5542</v>
       </c>
       <c r="E18" t="n">
-        <v>-21.3884</v>
+        <v>-18.0662</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.6687</v>
+        <v>-5.4879</v>
       </c>
       <c r="G18" t="n">
         <v>-7.5204</v>
@@ -1858,13 +1858,13 @@
         <v>33.1696</v>
       </c>
       <c r="S18" t="n">
-        <v>-16.0599</v>
+        <v>-7.557</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.5953</v>
+        <v>-6.2732</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.4648</v>
+        <v>-1.284</v>
       </c>
       <c r="V18" t="n">
         <v>-4.997800000000001</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>-32.4539</v>
+        <v>-25.5513</v>
       </c>
       <c r="E19" t="n">
-        <v>-37.807</v>
+        <v>-29.3772</v>
       </c>
       <c r="F19" t="n">
-        <v>5.352899999999999</v>
+        <v>3.8254</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4536</v>
+        <v>3.8186</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.9305</v>
+        <v>-4.8508</v>
       </c>
       <c r="I19" t="n">
-        <v>11.3841</v>
+        <v>8.6693</v>
       </c>
       <c r="J19" t="n">
-        <v>50.5943</v>
+        <v>28.969</v>
       </c>
       <c r="K19" t="n">
-        <v>16.6636</v>
+        <v>10.3077</v>
       </c>
       <c r="L19" t="n">
-        <v>33.9307</v>
+        <v>18.6612</v>
       </c>
       <c r="M19" t="n">
-        <v>-48.141</v>
+        <v>-25.1503</v>
       </c>
       <c r="N19" t="n">
-        <v>-25.5947</v>
+        <v>-15.1587</v>
       </c>
       <c r="O19" t="n">
-        <v>-22.5464</v>
+        <v>-9.9918</v>
       </c>
       <c r="P19" t="n">
-        <v>-18.7881</v>
+        <v>-14.6131</v>
       </c>
       <c r="Q19" t="n">
-        <v>-93.0129</v>
+        <v>-55.9006</v>
       </c>
       <c r="R19" t="n">
-        <v>74.22490000000001</v>
+        <v>41.2878</v>
       </c>
       <c r="S19" t="n">
-        <v>-28.7203</v>
+        <v>-2.1123</v>
       </c>
       <c r="T19" t="n">
-        <v>-23.5811</v>
+        <v>-4.5101</v>
       </c>
       <c r="U19" t="n">
-        <v>-5.139</v>
+        <v>2.3981</v>
       </c>
       <c r="V19" t="n">
-        <v>12.6002</v>
+        <v>-12.645</v>
       </c>
       <c r="W19" t="n">
-        <v>28.1919</v>
+        <v>2.0648</v>
       </c>
       <c r="X19" t="n">
-        <v>-15.5917</v>
+        <v>-14.7098</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>-35.1259</v>
+        <v>-25.8599</v>
       </c>
       <c r="E20" t="n">
-        <v>-37.7038</v>
+        <v>-17.3492</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5777</v>
+        <v>-8.5107</v>
       </c>
       <c r="G20" t="n">
-        <v>3.8186</v>
+        <v>-34.3241</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.8508</v>
+        <v>-13.311</v>
       </c>
       <c r="I20" t="n">
-        <v>8.6693</v>
+        <v>-21.0128</v>
       </c>
       <c r="J20" t="n">
-        <v>28.969</v>
+        <v>-3.0712</v>
       </c>
       <c r="K20" t="n">
-        <v>10.3077</v>
+        <v>0.9331</v>
       </c>
       <c r="L20" t="n">
-        <v>18.6612</v>
+        <v>-4.0044</v>
       </c>
       <c r="M20" t="n">
-        <v>-25.1503</v>
+        <v>-31.2528</v>
       </c>
       <c r="N20" t="n">
-        <v>-15.1587</v>
+        <v>-14.2442</v>
       </c>
       <c r="O20" t="n">
-        <v>-9.9918</v>
+        <v>-17.0087</v>
       </c>
       <c r="P20" t="n">
-        <v>-14.6131</v>
+        <v>16.7008</v>
       </c>
       <c r="Q20" t="n">
-        <v>-55.9006</v>
+        <v>-14.8452</v>
       </c>
       <c r="R20" t="n">
-        <v>41.2878</v>
+        <v>31.5457</v>
       </c>
       <c r="S20" t="n">
-        <v>-11.6867</v>
+        <v>-5.9502</v>
       </c>
       <c r="T20" t="n">
-        <v>-12.8378</v>
+        <v>-5.3614</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1509</v>
+        <v>-0.5888</v>
       </c>
       <c r="V20" t="n">
-        <v>-12.645</v>
+        <v>-2.2862</v>
       </c>
       <c r="W20" t="n">
-        <v>2.0648</v>
+        <v>5.9282</v>
       </c>
       <c r="X20" t="n">
-        <v>-14.7098</v>
+        <v>-8.214400000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>-35.465</v>
+        <v>-27.8433</v>
       </c>
       <c r="E21" t="n">
-        <v>-24.0293</v>
+        <v>-21.4024</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.436</v>
+        <v>-6.4406</v>
       </c>
       <c r="G21" t="n">
-        <v>-34.3241</v>
+        <v>-35.5159</v>
       </c>
       <c r="H21" t="n">
-        <v>-13.311</v>
+        <v>-16.3231</v>
       </c>
       <c r="I21" t="n">
-        <v>-21.0128</v>
+        <v>-19.1926</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.0712</v>
+        <v>-12.7585</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9331</v>
+        <v>-7.5473</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.0044</v>
+        <v>-5.2109</v>
       </c>
       <c r="M21" t="n">
-        <v>-31.2528</v>
+        <v>-22.7573</v>
       </c>
       <c r="N21" t="n">
-        <v>-14.2442</v>
+        <v>-8.7759</v>
       </c>
       <c r="O21" t="n">
-        <v>-17.0087</v>
+        <v>-13.9812</v>
       </c>
       <c r="P21" t="n">
-        <v>16.7008</v>
+        <v>5.798999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-14.8452</v>
+        <v>-16.2371</v>
       </c>
       <c r="R21" t="n">
-        <v>31.5457</v>
+        <v>22.0355</v>
       </c>
       <c r="S21" t="n">
-        <v>-15.5552</v>
+        <v>0.3585999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-12.0414</v>
+        <v>-1.6632</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.5138</v>
+        <v>2.0218</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2862</v>
+        <v>1.514999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>5.9282</v>
+        <v>9.2555</v>
       </c>
       <c r="X21" t="n">
-        <v>-8.214400000000001</v>
+        <v>-7.7404</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>38</v>
       </c>
       <c r="D22" t="n">
-        <v>-183.2652</v>
+        <v>-146.368</v>
       </c>
       <c r="E22" t="n">
-        <v>-125.2806</v>
+        <v>-116.6933</v>
       </c>
       <c r="F22" t="n">
-        <v>-57.98520000000001</v>
+        <v>-29.6777</v>
       </c>
       <c r="G22" t="n">
         <v>-157.4083</v>
@@ -2143,7 +2143,7 @@
         <v>-99.6414</v>
       </c>
       <c r="J22" t="n">
-        <v>244.7322</v>
+        <v>244.7322000000001</v>
       </c>
       <c r="K22" t="n">
         <v>141.5454</v>
@@ -2152,7 +2152,7 @@
         <v>103.1856</v>
       </c>
       <c r="M22" t="n">
-        <v>-402.1397</v>
+        <v>-402.1396999999999</v>
       </c>
       <c r="N22" t="n">
         <v>-199.3129</v>
@@ -2170,13 +2170,13 @@
         <v>570.607</v>
       </c>
       <c r="S22" t="n">
-        <v>-19.7692</v>
+        <v>17.1272</v>
       </c>
       <c r="T22" t="n">
-        <v>-42.7946</v>
+        <v>-34.2064</v>
       </c>
       <c r="U22" t="n">
-        <v>23.0256</v>
+        <v>51.3341</v>
       </c>
       <c r="V22" t="n">
         <v>-25.8051</v>
